--- a/out/analysis/testjuhtumid.xlsx
+++ b/out/analysis/testjuhtumid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testjuhtumid" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Testjuhtumid" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -140,19 +140,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestJuhtumid" displayName="TestJuhtumid" ref="A1:J6" headerRowCount="1">
-  <autoFilter ref="A1:J6"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestJuhtumid" displayName="TestJuhtumid" ref="A1:L6" headerRowCount="1">
+  <autoFilter ref="A1:L6"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Päring"/>
-    <tableColumn id="3" name="Filtrid"/>
-    <tableColumn id="4" name="Expected unique_ID (top_codes)"/>
-    <tableColumn id="5" name="Tulemus (PASS/FAIL)"/>
-    <tableColumn id="6" name="Märkus"/>
-    <tableColumn id="7" name="Logi aeg"/>
-    <tableColumn id="8" name="Logi tulemus"/>
-    <tableColumn id="9" name="Logi top_codes"/>
-    <tableColumn id="10" name="Expected vs Logi"/>
+    <tableColumn id="2" name="Expected vs Logi"/>
+    <tableColumn id="3" name="Expected"/>
+    <tableColumn id="4" name="Logi"/>
+    <tableColumn id="5" name="Päring"/>
+    <tableColumn id="6" name="Filtrid"/>
+    <tableColumn id="7" name="Expected unique_ID (top_codes)"/>
+    <tableColumn id="8" name="Tulemus (PASS/FAIL)"/>
+    <tableColumn id="9" name="Märkus"/>
+    <tableColumn id="10" name="Logi aeg"/>
+    <tableColumn id="11" name="Logi tulemus"/>
+    <tableColumn id="12" name="Logi top_codes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
 </table>
@@ -447,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -470,47 +472,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Expected vs Logi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Logi</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Päring</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Filtrid</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Expected unique_ID (top_codes)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Tulemus (PASS/FAIL)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Märkus</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Logi aeg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Logi tulemus</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Logi top_codes</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Expected vs Logi</t>
         </is>
       </c>
     </row>
@@ -522,47 +534,53 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Soovita 2 kursust järgmiste piirangutega: 4 EAP, inglise keeles, sügissemester, magistrile, (LT). Kui täpselt ei leia, paku lähimad alternatiivid ja ütle miks.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>credits=4, semester=autumn, language=en, level=master, faculty=LT</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>SVMJ.05.002, LTOM.03.021, ARFS.01.023, MVBS.07.004, LTBI.00.034</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Expected on valitud metadata-st sama filtrikombinatsiooni alt (mitte LLM output).</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-03-02 13:17:47</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:41:12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>SVMJ.05.002, LTOM.03.021, LTBI.00.034, LTKT.04.003, LTOM.02.051</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>HIT</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>SVMJ.05.002, LTOM.03.021, LTBI.00.034, LTKT.04.003, LTOM.02.051, LTKT.04.004</t>
         </is>
       </c>
     </row>
@@ -574,47 +592,53 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Mul on vaja semestriplaani. Leia 4 kursust filtritega: 3 EAP, eesti keeles, kevadsemester, bakalaureusele, (HV). nii, et töökoormus oleks mõistlik. Lisa iga kursuse juurde ka võimalik risk (nt raske matemaatika, palju rühmatööd).</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>credits=3, semester=spring, language=et, level=bachelor, faculty=HV</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>FLSE.00.311, HVEE.05.040, HVEE.05.041, LOKT.02.041, MJRI.03.099</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Expected on valitud metadata-st sama filtrikombinatsiooni alt (mitte LLM output).</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-03-02 13:19:11</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:41:23</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>FLSE.00.311, HVEE.05.040, HVEE.05.041, LOKT.02.041, MJRI.03.099</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>HIT</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>FLSE.00.311, HVEE.05.040, HVEE.05.041, LOKT.02.041, MJRI.03.099, FLSE.00.054, FLEE.02.042, LTAT.00.007, FLGR.03.136, FLGR.01.042</t>
         </is>
       </c>
     </row>
@@ -626,47 +650,53 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Palun koosta lühike shortlist: 5 sobivaimat kursust tingimustega: 3 EAP, eesti keeles, sügissemester, bakalaureusele, (LT). Väldi liiga teoreetilisi aineid; eelista praktilisi.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>credits=3, semester=autumn, language=et, level=bachelor, faculty=LT</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>HVEE.00.019, HVEE.02.005, LTFY.01.001, LOTI.05.021, LTAT.01.004</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Expected on valitud metadata-st sama filtrikombinatsiooni alt (mitte LLM output).</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-03-02 13:19:46</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:41:37</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>HVEE.00.019, HVEE.02.005, LTFY.01.001, LOTI.05.021, LTAT.01.004</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>HIT</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>HVEE.00.019, HVEE.02.005, LTFY.01.001, LOTI.05.021, LTAT.01.004, LTFY.01.028, LTKT.00.010, FLGR.03.205, SVNC.00.130, HVLC.01.008</t>
         </is>
       </c>
     </row>
@@ -678,47 +708,53 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Soovita 2 kursust tingimustega: 6 EAP, eesti keeles, sügissemester, bakalaureusele, (HV). Kui täpselt ei leia, paku lähimad alternatiivid ja ütle miks.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>credits=6, semester=autumn, language=et, level=bachelor, faculty=HV</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>FLLC.09.007, HVLC.09.038, FLLC.09.006</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Expected on valitud metadata-st sama filtrikombinatsiooni alt (mitte LLM output).</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-03-02 13:20:21</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:41:48</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>FLLC.09.007, HVLC.09.038, FLLC.09.006, HVLC.09.056, HVLC.01.027</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>HIT</t>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>FLLC.09.007, HVLC.09.038, FLLC.09.006, HVLC.09.056, HVLC.01.027, HVLC.09.055, FLFI.05.025, HVLC.01.052, HVLC.01.029, HVEE.04.004</t>
         </is>
       </c>
     </row>
@@ -730,47 +766,53 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Olen valimas aineid. Soovita 5 kursust (soovid: 3 EAP, eesti keeles, sügissemester, bakalaureusele, (LT). Iga soovituse juurde lisa: kood, 1–2 lauset miks see sobib, ja mida eeldatakse eelteadmistena.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>credits=3, semester=autumn, language=et, level=bachelor, faculty=LT</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>HVEE.00.019, LTFY.01.028, HVEE.02.005, LTFY.01.001, LTKT.00.010</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Expected on valitud metadata-st sama filtrikombinatsiooni alt (mitte LLM output).</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-03-02 13:20:47</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-03-05 13:42:17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>HVEE.00.019, LTFY.01.028, HVEE.02.005, LTFY.01.001, LTKT.00.010</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>HIT</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>HVEE.00.019, LTFY.01.028, HVEE.02.005, LTFY.01.001, LTKT.00.010, HVLC.01.008, FLEE.08.001, FLEE.02.017, LTOM.03.048, SVNC.00.130</t>
         </is>
       </c>
     </row>

--- a/out/analysis/testjuhtumid.xlsx
+++ b/out/analysis/testjuhtumid.xlsx
@@ -534,28 +534,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Soovita 2 kursust järgmiste piirangutega: 4 EAP, inglise keeles, sügissemester, magistrile, (LT). Kui täpselt ei leia, paku lähimad alternatiivid ja ütle miks.</t>
+          <t>Olen valimas aineid. Soovita 4 kursust informaatika/andmeteaduse suunal (soovid: 3 EAP, eesti keeles, sügissemester. Iga soovituse juurde lisa: kood, 1–2 lauset miks see sobib, ja mida eeldatakse eelteadmistena.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>credits=4, semester=autumn, language=en, level=master, faculty=LT</t>
+          <t>credits=3, semester=autumn, language=et, level=ANY, faculty=HV</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SVMJ.05.002, LTOM.03.021, ARFS.01.023, MVBS.07.004, LTBI.00.034</t>
+          <t>MTAT.03.312, HVLC.01.008, LOOM.02.044, LOMR.10.002, LOMR.10.005, LOOM.02.006, HVEE.02.005, FLSE.00.058, MTMS.01.016, MTAT.03.105</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-03-05 13:41:12</t>
+          <t>2026-03-05 14:00:59</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SVMJ.05.002, LTOM.03.021, LTBI.00.034, LTKT.04.003, LTOM.02.051, LTKT.04.004</t>
+          <t>MTAT.03.312, HVLC.01.008, LOOM.02.044, LOMR.10.002, LOMR.10.005, LOOM.02.006, HVEE.02.005, FLSE.00.058, MTMS.01.016, MTAT.03.105</t>
         </is>
       </c>
     </row>
@@ -592,28 +592,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mul on vaja semestriplaani. Leia 4 kursust filtritega: 3 EAP, eesti keeles, kevadsemester, bakalaureusele, (HV). nii, et töökoormus oleks mõistlik. Lisa iga kursuse juurde ka võimalik risk (nt raske matemaatika, palju rühmatööd).</t>
+          <t>Otsin 3 kursust praktilise IT suunal järgmiste piirangutega: 6 EAP, eesti keeles, sügissemester, bakalaureusele, (HV). Tee valik nii, et kursused oleksid omavahel võimalikult erinevad.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>credits=3, semester=spring, language=et, level=bachelor, faculty=HV</t>
+          <t>credits=6, semester=autumn, language=et, level=bachelor, faculty=HV</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FLSE.00.311, HVEE.05.040, HVEE.05.041, LOKT.02.041, MJRI.03.099</t>
+          <t>MTAT.03.237, HVLC.09.038, P2NC.00.946, LTAT.06.001, HVEE.04.004, FLLC.09.006, HVLC.09.055, HVLC.09.056</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-05 13:41:23</t>
+          <t>2026-03-05 14:01:09</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FLSE.00.311, HVEE.05.040, HVEE.05.041, LOKT.02.041, MJRI.03.099, FLSE.00.054, FLEE.02.042, LTAT.00.007, FLGR.03.136, FLGR.01.042</t>
+          <t>MTAT.03.237, HVLC.09.038, P2NC.00.946, LTAT.06.001, HVEE.04.004, FLLC.09.006, HVLC.09.055, HVLC.09.056, FLLC.09.007, SVNC.00.070</t>
         </is>
       </c>
     </row>
@@ -650,28 +650,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Palun koosta lühike shortlist: 5 sobivaimat kursust tingimustega: 3 EAP, eesti keeles, sügissemester, bakalaureusele, (LT). Väldi liiga teoreetilisi aineid; eelista praktilisi.</t>
+          <t>Otsin 2 kursust praktilise IT suunal filtritega: 3 EAP, eesti keeles, kevadsemester. Tee valik nii, et kursused oleksid omavahel võimalikult erinevad.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>credits=3, semester=autumn, language=et, level=bachelor, faculty=LT</t>
+          <t>credits=3, semester=spring, language=et, level=ANY, faculty=HV</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HVEE.00.019, HVEE.02.005, LTFY.01.001, LOTI.05.021, LTAT.01.004</t>
+          <t>FLEE.04.124, HVLC.07.002, HVEE.05.041, HTOS.02.233, HVEE.00.043, MTAT.07.028, FLEE.02.042</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-05 13:41:37</t>
+          <t>2026-03-05 14:01:13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>HVEE.00.019, HVEE.02.005, LTFY.01.001, LOTI.05.021, LTAT.01.004, LTFY.01.028, LTKT.00.010, FLGR.03.205, SVNC.00.130, HVLC.01.008</t>
+          <t>FLEE.04.124, HVEE.05.041, HTOS.02.233, HVEE.00.043, FLEE.02.042, HVEE.05.040, HVLC.07.002, HVVK.12.068, HVLC.01.003, FLGR.06.167</t>
         </is>
       </c>
     </row>
@@ -708,28 +708,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Soovita 2 kursust tingimustega: 6 EAP, eesti keeles, sügissemester, bakalaureusele, (HV). Kui täpselt ei leia, paku lähimad alternatiivid ja ütle miks.</t>
+          <t>Otsin 4 kursust analüüsi ja modelleerimise suunal järgmiste piirangutega: 3 EAP, eesti keeles, sügissemester, bakalaureusele, (HV). Tee valik nii, et kursused oleksid omavahel võimalikult erinevad.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>credits=6, semester=autumn, language=et, level=bachelor, faculty=HV</t>
+          <t>credits=3, semester=autumn, language=et, level=bachelor, faculty=HV</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FLLC.09.007, HVLC.09.038, FLLC.09.006</t>
+          <t>HVEE.02.005, LOFY.03.084, HVLC.01.010, MJRI.09.002, LTFY.01.028, HVLC.05.010, MTMM.00.242, LTKT.00.010, HVEE.00.019</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-05 13:41:48</t>
+          <t>2026-03-05 14:01:32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FLLC.09.007, HVLC.09.038, FLLC.09.006, HVLC.09.056, HVLC.01.027, HVLC.09.055, FLFI.05.025, HVLC.01.052, HVLC.01.029, HVEE.04.004</t>
+          <t>MTMM.00.251, HVEE.02.005, LOFY.03.084, HVLC.01.010, MJRI.09.002, LTFY.01.028, HVLC.05.010, MTMM.00.242, LTKT.00.010, HVEE.00.019</t>
         </is>
       </c>
     </row>
@@ -766,28 +766,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5/5</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olen valimas aineid. Soovita 5 kursust (soovid: 3 EAP, eesti keeles, sügissemester, bakalaureusele, (LT). Iga soovituse juurde lisa: kood, 1–2 lauset miks see sobib, ja mida eeldatakse eelteadmistena.</t>
+          <t>Otsin 2 kursust analüüsi ja modelleerimise suunal (soovid: 3 EAP, eesti keeles, kevadsemester, bakalaureusele, (LT). Tee valik nii, et kursused oleksid omavahel võimalikult erinevad.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>credits=3, semester=autumn, language=et, level=bachelor, faculty=LT</t>
+          <t>credits=3, semester=spring, language=et, level=bachelor, faculty=LT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HVEE.00.019, LTFY.01.028, HVEE.02.005, LTFY.01.001, LTKT.00.010</t>
+          <t>FLGR.05.395, FLSE.00.054, HTOS.02.233, LOFY.05.025, HVEE.05.041, FLGR.05.263, LOOM.03.010, P2NC.00.017, LOKT.04.075, LTAT.03.023</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-05 13:42:17</t>
+          <t>2026-03-05 14:01:39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>HVEE.00.019, LTFY.01.028, HVEE.02.005, LTFY.01.001, LTKT.00.010, HVLC.01.008, FLEE.08.001, FLEE.02.017, LTOM.03.048, SVNC.00.130</t>
+          <t>FLGR.05.395, FLSE.00.054, LOFY.05.025, HVEE.05.041, FLGR.05.263, LOOM.03.010, P2NC.00.017, LOKT.04.075, LTAT.03.023, HVEE.05.040</t>
         </is>
       </c>
     </row>

--- a/out/analysis/testjuhtumid.xlsx
+++ b/out/analysis/testjuhtumid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Testjuhtumid" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testjuhtumid" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,17 +545,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Olen valimas aineid. Soovita 4 kursust informaatika/andmeteaduse suunal (soovid: 3 EAP, eesti keeles, sügissemester. Iga soovituse juurde lisa: kood, 1–2 lauset miks see sobib, ja mida eeldatakse eelteadmistena.</t>
+          <t>Mul on vaja semestriplaani. Leia 4 kursust praktilise IT suunal (soovid: 3 EAP, eesti keeles, sügissemester, bakalaureusele. nii, et töökoormus oleks mõistlik. Lisa iga kursuse juurde ka võimalik risk (nt raske matemaatika, palju rühmatööd).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>credits=3, semester=autumn, language=et, level=ANY, faculty=HV</t>
+          <t>credits=3, semester=autumn, language=et, level=bachelor, faculty=LT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MTAT.03.312, HVLC.01.008, LOOM.02.044, LOMR.10.002, LOMR.10.005, LOOM.02.006, HVEE.02.005, FLSE.00.058, MTMS.01.016, MTAT.03.105</t>
+          <t>MJRI.02.065, LOTI.05.021, FLGR.03.160, LOFY.02.063, LOFY.03.001, HVLC.01.008, LTFY.01.028, LTFY.01.001, FLFI.00.106, LTOM.03.048</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-03-05 14:00:59</t>
+          <t>2026-03-05 16:28:57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MTAT.03.312, HVLC.01.008, LOOM.02.044, LOMR.10.002, LOMR.10.005, LOOM.02.006, HVEE.02.005, FLSE.00.058, MTMS.01.016, MTAT.03.105</t>
+          <t>MJRI.02.065, LOTI.05.021, FLGR.03.160, LOFY.02.063, LOFY.03.001, HVLC.01.008, LTFY.01.028, LTFY.01.001, FLFI.00.106, LTOM.03.048</t>
         </is>
       </c>
     </row>
@@ -592,28 +592,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Otsin 3 kursust praktilise IT suunal järgmiste piirangutega: 6 EAP, eesti keeles, sügissemester, bakalaureusele, (HV). Tee valik nii, et kursused oleksid omavahel võimalikult erinevad.</t>
+          <t>Mul on vaja semestriplaani. Leia 2 kursust analüüsi ja modelleerimise suunal järgmiste piirangutega: 3 EAP, eesti keeles, sügissemester, bakalaureusele, (HV). nii, et töökoormus oleks mõistlik. Lisa iga kursuse juurde ka võimalik risk (nt raske matemaatika, palju rühmatööd).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>credits=6, semester=autumn, language=et, level=bachelor, faculty=HV</t>
+          <t>credits=3, semester=autumn, language=et, level=bachelor, faculty=HV</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MTAT.03.237, HVLC.09.038, P2NC.00.946, LTAT.06.001, HVEE.04.004, FLLC.09.006, HVLC.09.055, HVLC.09.056</t>
+          <t>FLGR.03.160, MJRI.09.002, HTOS.02.455, HVLC.01.010, MJRI.02.065, SHHI.02.050, FLGR.03.205, MTMM.00.242, LTOM.03.048, HVLC.05.010</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-05 14:01:09</t>
+          <t>2026-03-05 16:29:10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MTAT.03.237, HVLC.09.038, P2NC.00.946, LTAT.06.001, HVEE.04.004, FLLC.09.006, HVLC.09.055, HVLC.09.056, FLLC.09.007, SVNC.00.070</t>
+          <t>FLGR.03.160, MJRI.09.002, HTOS.02.455, HVLC.01.010, MJRI.02.065, MTMM.00.251, FLGR.03.205, MTMM.00.242, LTOM.03.048, HVLC.05.010</t>
         </is>
       </c>
     </row>
@@ -650,28 +650,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Otsin 2 kursust praktilise IT suunal filtritega: 3 EAP, eesti keeles, kevadsemester. Tee valik nii, et kursused oleksid omavahel võimalikult erinevad.</t>
+          <t>Soovita 4 kursust informaatika/andmeteaduse suunal tingimustega: 6 EAP, inglise keeles, kevadsemester, magistrile, (HV). Kui täpselt ei leia, paku lähimad alternatiivid ja ütle miks.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>credits=3, semester=spring, language=et, level=ANY, faculty=HV</t>
+          <t>credits=6, semester=spring, language=en, level=master, faculty=HV</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FLEE.04.124, HVLC.07.002, HVEE.05.041, HTOS.02.233, HVEE.00.043, MTAT.07.028, FLEE.02.042</t>
+          <t>HVLC.05.069, LTBI.00.027, MTAT.03.325, SORG.04.023, LTBI.00.019, MTAT.03.239, HVLC.09.065, LTTO.00.028, LTAT.06.019, LTAT.02.036</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-05 14:01:13</t>
+          <t>2026-03-05 16:29:24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FLEE.04.124, HVEE.05.041, HTOS.02.233, HVEE.00.043, FLEE.02.042, HVEE.05.040, HVLC.07.002, HVVK.12.068, HVLC.01.003, FLGR.06.167</t>
+          <t>HVLC.09.029, HVLC.05.069, FLLC.09.002, LTBI.00.027, MTAT.03.325, SORG.04.023, LTBI.00.019, MTAT.03.239, HVLC.09.065, LTTO.00.028</t>
         </is>
       </c>
     </row>
@@ -708,28 +708,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Otsin 4 kursust analüüsi ja modelleerimise suunal järgmiste piirangutega: 3 EAP, eesti keeles, sügissemester, bakalaureusele, (HV). Tee valik nii, et kursused oleksid omavahel võimalikult erinevad.</t>
+          <t>Olen valimas aineid. Soovita 5 kursust informaatika/andmeteaduse suunal (soovid: 3 EAP, eesti keeles, kevadsemester, bakalaureusele. Iga soovituse juurde lisa: kood, 1–2 lauset miks see sobib, ja mida eeldatakse eelteadmistena.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>credits=3, semester=autumn, language=et, level=bachelor, faculty=HV</t>
+          <t>credits=3, semester=spring, language=et, level=bachelor, faculty=LT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HVEE.02.005, LOFY.03.084, HVLC.01.010, MJRI.09.002, LTFY.01.028, HVLC.05.010, MTMM.00.242, LTKT.00.010, HVEE.00.019</t>
+          <t>SVUH.00.271, MTAT.07.028, MTMS.02.040, FLEE.08.145, HVLC.05.032, FLSE.00.054, HVEE.01.004, MJJV.03.172</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-05 14:01:32</t>
+          <t>2026-03-05 16:29:42</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>MTMM.00.251, HVEE.02.005, LOFY.03.084, HVLC.01.010, MJRI.09.002, LTFY.01.028, HVLC.05.010, MTMM.00.242, LTKT.00.010, HVEE.00.019</t>
+          <t>MTAT.07.028, SVUH.00.271, MTMS.02.040, FLEE.08.145, HVLC.05.032, FLSE.00.054, HVEE.01.004, LOTI.05.042, HVLC.02.005, LTOM.02.034</t>
         </is>
       </c>
     </row>
@@ -766,28 +766,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Otsin 2 kursust analüüsi ja modelleerimise suunal (soovid: 3 EAP, eesti keeles, kevadsemester, bakalaureusele, (LT). Tee valik nii, et kursused oleksid omavahel võimalikult erinevad.</t>
+          <t>Palun koosta lühike shortlist: 3 sobivaimat kursust ettevõtluse ja digilahenduste suunal järgmiste piirangutega: 6 EAP, inglise keeles, sügissemester, bakalaureusele, (HV). Eelista praktilisi aineid ning maini, milline oskus igast kursusest kaasa tuleb.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>credits=3, semester=spring, language=et, level=bachelor, faculty=LT</t>
+          <t>credits=6, semester=autumn, language=en, level=bachelor, faculty=HV</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FLGR.05.395, FLSE.00.054, HTOS.02.233, LOFY.05.025, HVEE.05.041, FLGR.05.263, LOOM.03.010, P2NC.00.017, LOKT.04.075, LTAT.03.023</t>
+          <t>HVLC.09.029, LTAT.05.004, LTMR.00.001, MJRI.02.074, FLLC.09.002, P2NC.00.680, LOTI.05.103</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-03-05 14:01:39</t>
+          <t>2026-03-05 16:29:55</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FLGR.05.395, FLSE.00.054, LOFY.05.025, HVEE.05.041, FLGR.05.263, LOOM.03.010, P2NC.00.017, LOKT.04.075, LTAT.03.023, HVEE.05.040</t>
+          <t>HVLC.09.029, LTAT.05.004, LTMR.00.001, MJRI.02.074, FLLC.09.002, HVLC.01.077, HVLC.05.013, MJJV.10.044, LOTI.05.106, MJJV.09.031</t>
         </is>
       </c>
     </row>
